--- a/data/NREL-118/Power_Network.xlsx
+++ b/data/NREL-118/Power_Network.xlsx
@@ -13,7 +13,7 @@
     <workbookView xWindow="34230" yWindow="-21705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="scenarioA" sheetId="1" r:id="rId1"/>
+    <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
